--- a/data/Scan_Log_Dataset.xlsx
+++ b/data/Scan_Log_Dataset.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M110"/>
+  <dimension ref="A1:M111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43.28515625" customWidth="1" min="1" max="1"/>
@@ -5996,6 +5996,61 @@
         <v>4</v>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>test project</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>5</v>
+      </c>
+      <c r="E111" t="n">
+        <v>5</v>
+      </c>
+      <c r="F111" t="n">
+        <v>5</v>
+      </c>
+      <c r="G111" t="n">
+        <v>2</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="K111" t="n">
+        <v>1</v>
+      </c>
+      <c r="L111" t="n">
+        <v>777</v>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>2026-07-07 13:45:25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>

--- a/data/Scan_Log_Dataset.xlsx
+++ b/data/Scan_Log_Dataset.xlsx
@@ -995,6 +995,11 @@
       <c r="L10" t="n">
         <v>617</v>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-07-07 13:59:19</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">

--- a/data/Scan_Log_Dataset.xlsx
+++ b/data/Scan_Log_Dataset.xlsx
@@ -595,6 +595,11 @@
       <c r="L2" t="n">
         <v>435</v>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-07-07 14:12:48</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
